--- a/INSTANCES/instances_xlsx/A_MTN_5/379FL_15A_1.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_5/379FL_15A_1.xlsx
@@ -12020,7 +12020,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -12037,7 +12037,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -12054,7 +12054,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -12088,7 +12088,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -12105,7 +12105,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -12122,7 +12122,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -12139,7 +12139,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -12173,7 +12173,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -12224,7 +12224,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -12258,7 +12258,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>1</v>
